--- a/tmall_profit_analysis.xlsx
+++ b/tmall_profit_analysis.xlsx
@@ -16,6 +16,7 @@
     <sheet name="数据源" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="周报其他费用" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="07-修订说明" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="08-一致性核对" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'06-全量ID每周净利润'!$A$4:$N$56</definedName>
@@ -28,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,8 +73,29 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="001A237E"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -100,8 +122,23 @@
         <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00263238"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -167,11 +204,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -213,6 +264,26 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -291,7 +362,6 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
   <chart>
     <title>
       <tx>
@@ -834,7 +904,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>巴东链接费率32%–38%，属推广费过高型亏损；原味大大包需控加投侵蚀，但不是主亏源。</t>
+          <t>巴东链接推广费率约21%–36%（按品名/定位含巴东，成交&gt;500周），属推广费偏高型亏损；原味大大包需控加投侵蚀，但不是主亏源。另：部分ID跨周改品，专题请看「08-一致性核对」。</t>
         </is>
       </c>
       <c r="C13" s="8" t="n"/>
@@ -1284,8 +1354,8 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A18:H18"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="B13:H13"/>
     <mergeCell ref="A20:H20"/>
@@ -1297,6 +1367,652 @@
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="B11:H11"/>
     <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="27" t="inlineStr">
+        <is>
+          <t>数据一致性核对（自动检查结果）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>核对日期：2026-08-13｜口径：推广后=推广前-(推广总花费+其他费用)/1.06；其他费用=周报×件数占比</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="28" t="inlineStr">
+        <is>
+          <t>一、硬核对（金额口径）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>检查项</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>结果</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="D5" s="23" t="inlineStr">
+        <is>
+          <t>关键数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>各周其他费用合计=周报</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr">
+        <is>
+          <t>按件数占比分摊后周合计应等于周报输入</t>
+        </is>
+      </c>
+      <c r="D6" s="29" t="inlineStr">
+        <is>
+          <t>5.11-5.17:1911.0; 5.25-5.31:1911.0; 6.15-6.21:3605.0; 6.22-6.28:3605.0; 6.29-7.5:1951.0; 7.6-7.12:2054.0; 7.13-7.19:2405.0; 7.20-7.26:2097.0; 7.27-8.2:2127.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="inlineStr">
+        <is>
+          <t>推广后利润公式口径</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
+        <is>
+          <t>逐行 after=pre-(spend+fee)/1.06 可闭合到周汇总</t>
+        </is>
+      </c>
+      <c r="D7" s="29" t="inlineStr">
+        <is>
+          <t>9周推广后合计=-55027.4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>最好一周=7.6-7.12</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="inlineStr">
+        <is>
+          <t>与汇报摘要结论1一致</t>
+        </is>
+      </c>
+      <c r="D8" s="29" t="inlineStr">
+        <is>
+          <t>7.6-7.12 = -4109.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="inlineStr">
+        <is>
+          <t>7.6→7.13 利润额主因</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="inlineStr">
+        <is>
+          <t>摘要写「偏推广前下降」；同期花费实际下降、对利润为正贡献</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="inlineStr">
+        <is>
+          <t>Δ后=-1072.4; Δ前=-3190.6; 花费效应=2449.4; 其他费效应=-331.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>7.13→7.20 利润额主因</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="inlineStr">
+        <is>
+          <t>摘要写「主因推广费上升」</t>
+        </is>
+      </c>
+      <c r="D10" s="29" t="inlineStr">
+        <is>
+          <t>Δ后=-432.2; Δ前=-150.1; 花费效应=-572.6; 其他费效应=290.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>巴东费率「32%–38%」旧表述</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="inlineStr">
+        <is>
+          <t>旧摘要偏高；已改为按周实测区间（成交&gt;500）</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="inlineStr">
+        <is>
+          <t>实测约 20.5%–35.9%；各周=6.22-6.28:30.0%, 6.29-7.5:35.9%, 7.13-7.19:25.3%, 7.20-7.26:23.1%, 7.27-8.2:29.9%, 7.6-7.12:20.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="inlineStr">
+        <is>
+          <t>同义定位归一</t>
+        </is>
+      </c>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>FIXED</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="inlineStr">
+        <is>
+          <t>大大→原味大包，巴东→巴东牛肉，韩火鸡→韩式火鸡</t>
+        </is>
+      </c>
+      <c r="D12" s="29" t="inlineStr">
+        <is>
+          <t>本次数改写 6 行定位</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>ID跨周改品（品名+定位家族变化）</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>WARN</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="inlineStr">
+        <is>
+          <t>同一商品ID在不同周挂不同品类；ID利润仍可加总，但「按定位专题/环比归因」会串品</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="inlineStr">
+        <is>
+          <t>共 16 个ID，详见下方明细</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="28" t="inlineStr">
+        <is>
+          <t>二、ID跨周改品明细（主要矛盾）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>商品ID</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>品类家族</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>累计成交</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>各周：品类(定位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="inlineStr">
+        <is>
+          <t>648600900806</t>
+        </is>
+      </c>
+      <c r="B18" s="32" t="inlineStr">
+        <is>
+          <t>30包,巴东</t>
+        </is>
+      </c>
+      <c r="C18" s="32" t="n">
+        <v>79475.60000000001</v>
+      </c>
+      <c r="D18" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:30包(30包); 5.25-5.31:30包(30包); 6.15-6.21:30包(30包); 6.22-6.28:30包(30包); 6.29-7.5:30包(30包); 7.13-7.19:30包(30包); 7.20-7.26:30包(30包); 7.27-8.2:30包(30包); 7.6-7.12:巴东(巴东牛肉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="32" t="inlineStr">
+        <is>
+          <t>648598580775</t>
+        </is>
+      </c>
+      <c r="B19" s="32" t="inlineStr">
+        <is>
+          <t>15包,原味大大</t>
+        </is>
+      </c>
+      <c r="C19" s="32" t="n">
+        <v>30375.8</v>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:15包(15包); 5.25-5.31:15包(15包); 6.15-6.21:15包(15包); 6.22-6.28:15包(15包); 6.29-7.5:15包(15包); 7.13-7.19:原味大大(原味大包); 7.20-7.26:原味大大(原味大包); 7.27-8.2:原味大大(原味大包); 7.6-7.12:15包(15包)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="32" t="inlineStr">
+        <is>
+          <t>1058280415678</t>
+        </is>
+      </c>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>原味大大,巴东</t>
+        </is>
+      </c>
+      <c r="C20" s="32" t="n">
+        <v>18733.2</v>
+      </c>
+      <c r="D20" s="32" t="inlineStr">
+        <is>
+          <t>6.22-6.28:原味大大(原味大包); 6.29-7.5:原味大大(原味大包); 7.13-7.19:巴东(巴东牛肉); 7.20-7.26:巴东(巴东牛肉); 7.27-8.2:原味大大(原味大包); 7.6-7.12:原味大大(原味大包)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="32" t="inlineStr">
+        <is>
+          <t>766165464414</t>
+        </is>
+      </c>
+      <c r="B21" s="32" t="inlineStr">
+        <is>
+          <t>12包,巴东</t>
+        </is>
+      </c>
+      <c r="C21" s="32" t="n">
+        <v>13725.3</v>
+      </c>
+      <c r="D21" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:12包(12包); 5.25-5.31:12包(12包); 6.15-6.21:12包(12包); 6.22-6.28:12包(12包); 6.29-7.5:12包(12包); 7.13-7.19:12包(12包); 7.20-7.26:12包(12包); 7.27-8.2:12包(12包); 7.6-7.12:巴东(巴东牛肉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="32" t="inlineStr">
+        <is>
+          <t>648681860568</t>
+        </is>
+      </c>
+      <c r="B22" s="32" t="inlineStr">
+        <is>
+          <t>原味大大,巴东,杯面</t>
+        </is>
+      </c>
+      <c r="C22" s="32" t="n">
+        <v>11161.9</v>
+      </c>
+      <c r="D22" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:杯面(杯面次链接); 5.25-5.31:杯面(杯面次链接); 6.15-6.21:杯面(杯面次链接); 6.22-6.28:杯面(杯面次链接); 6.29-7.5:杯面(杯面次链接); 7.13-7.19:巴东(巴东牛肉); 7.20-7.26:杯面(杯面次链接); 7.27-8.2:杯面(杯面次链接); 7.6-7.12:原味大大(原味大包)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>1013887677295</t>
+        </is>
+      </c>
+      <c r="B23" s="32" t="inlineStr">
+        <is>
+          <t>原味大大,杯面</t>
+        </is>
+      </c>
+      <c r="C23" s="32" t="n">
+        <v>10252.9</v>
+      </c>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:杯面(混搭5杯); 5.25-5.31:杯面(混搭5杯); 6.15-6.21:杯面(混搭5杯); 6.22-6.28:杯面(混搭5杯); 6.29-7.5:杯面(混搭5杯); 7.13-7.19:杯面(混搭5杯); 7.20-7.26:原味大大(原味大包); 7.27-8.2:原味大大(原味大包); 7.6-7.12:杯面(混搭5杯)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="32" t="inlineStr">
+        <is>
+          <t>929504658691</t>
+        </is>
+      </c>
+      <c r="B24" s="32" t="inlineStr">
+        <is>
+          <t>巴东,袋面其他</t>
+        </is>
+      </c>
+      <c r="C24" s="32" t="n">
+        <v>6591.5</v>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:袋面其他(日式袋面); 5.25-5.31:袋面其他(日式袋面); 6.15-6.21:袋面其他(日式袋面); 6.22-6.28:袋面其他(日韩袋面); 6.29-7.5:袋面其他(日式袋面); 7.13-7.19:袋面其他(日式袋面); 7.20-7.26:巴东(巴东牛肉); 7.27-8.2:巴东(巴东牛肉); 7.6-7.12:袋面其他(日式袋面)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="32" t="inlineStr">
+        <is>
+          <t>1059563993918</t>
+        </is>
+      </c>
+      <c r="B25" s="32" t="inlineStr">
+        <is>
+          <t>原味大大,巴东</t>
+        </is>
+      </c>
+      <c r="C25" s="32" t="n">
+        <v>2658.5</v>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>6.22-6.28:巴东(巴东牛肉); 6.29-7.5:巴东(巴东牛肉); 7.13-7.19:原味大大(原味大包); 7.20-7.26:巴东(巴东牛肉); 7.27-8.2:巴东(巴东牛肉); 7.6-7.12:巴东(巴东牛肉)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="32" t="inlineStr">
+        <is>
+          <t>932687928859</t>
+        </is>
+      </c>
+      <c r="B26" s="32" t="inlineStr">
+        <is>
+          <t>杯面,袋面其他</t>
+        </is>
+      </c>
+      <c r="C26" s="32" t="n">
+        <v>694.4</v>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:袋面其他(8包组合); 6.15-6.21:袋面其他(8包组合); 6.22-6.28:袋面其他(8包组合); 6.29-7.5:袋面其他(8包组合); 7.13-7.19:袋面其他(8包组合); 7.20-7.26:袋面其他(8包组合); 7.27-8.2:杯面(杯面混搭); 7.6-7.12:袋面其他(8包组合)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="32" t="inlineStr">
+        <is>
+          <t>903183018417</t>
+        </is>
+      </c>
+      <c r="B27" s="32" t="inlineStr">
+        <is>
+          <t>七口味混搭,杯面</t>
+        </is>
+      </c>
+      <c r="C27" s="32" t="n">
+        <v>533.6</v>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:七口味混搭(七口味混搭); 5.25-5.31:七口味混搭(七口味混搭); 6.15-6.21:七口味混搭(七口味混搭); 6.22-6.28:七口味混搭(七口味混搭); 6.29-7.5:七口味混搭(七口味混搭); 7.13-7.19:七口味混搭(七口味混搭); 7.20-7.26:杯面(杯面混搭); 7.27-8.2:七口味混搭(七口味混搭); 7.6-7.12:七口味混搭(七口味混搭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="32" t="inlineStr">
+        <is>
+          <t>976479938842</t>
+        </is>
+      </c>
+      <c r="B28" s="32" t="inlineStr">
+        <is>
+          <t>【U选】原味5,杯面</t>
+        </is>
+      </c>
+      <c r="C28" s="32" t="n">
+        <v>507.3</v>
+      </c>
+      <c r="D28" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:【U选】原味5(【U选】原味5); 5.25-5.31:【U选】原味5(【U选】原味5); 6.15-6.21:【U选】原味5(【U选】原味5); 6.22-6.28:【U选】原味5(【U选】原味5); 6.29-7.5:【U选】原味5(【U选】原味5); 7.13-7.19:【U选】原味5(【U选】原味5); 7.20-7.26:杯面(杯面混搭); 7.27-8.2:【U选】原味5(【U选】原味5); 7.6-7.12:【U选】原味5(【U选】原味5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="32" t="inlineStr">
+        <is>
+          <t>949962665617</t>
+        </is>
+      </c>
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>组合,袋面其他</t>
+        </is>
+      </c>
+      <c r="C29" s="32" t="n">
+        <v>388.1</v>
+      </c>
+      <c r="D29" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:组合(组合); 5.25-5.31:组合(组合); 6.15-6.21:组合(组合); 6.29-7.5:组合(组合); 7.6-7.12:袋面其他(韩式袋面)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>898120785283</t>
+        </is>
+      </c>
+      <c r="B30" s="32" t="inlineStr">
+        <is>
+          <t>十全十美,番茄,袋面其他</t>
+        </is>
+      </c>
+      <c r="C30" s="32" t="n">
+        <v>296.3</v>
+      </c>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:番茄(番茄); 5.25-5.31:番茄(番茄); 6.15-6.21:番茄(番茄); 6.22-6.28:番茄(番茄); 6.29-7.5:番茄(番茄); 7.13-7.19:十全十美(十全十美); 7.27-8.2:番茄(番茄); 7.6-7.12:袋面其他(韩式袋面)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>965545088099</t>
+        </is>
+      </c>
+      <c r="B31" s="32" t="inlineStr">
+        <is>
+          <t>十全十美,十口味混搭</t>
+        </is>
+      </c>
+      <c r="C31" s="32" t="n">
+        <v>163.9</v>
+      </c>
+      <c r="D31" s="32" t="inlineStr">
+        <is>
+          <t>5.25-5.31:十口味混搭(十口味混搭); 6.29-7.5:十全十美(十全十美); 7.27-8.2:十口味混搭(十口味混搭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>976467954327</t>
+        </is>
+      </c>
+      <c r="B32" s="32" t="inlineStr">
+        <is>
+          <t>十全十美,杯面</t>
+        </is>
+      </c>
+      <c r="C32" s="32" t="n">
+        <v>158.6</v>
+      </c>
+      <c r="D32" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:杯面(日韩杯面); 5.25-5.31:杯面(日韩杯面); 6.22-6.28:杯面(【U选】韩式蘑菇1+日式辣杯1); 6.29-7.5:杯面(日韩杯面); 7.13-7.19:杯面(日韩杯面); 7.20-7.26:杯面(日韩杯面); 7.27-8.2:杯面(日韩杯面); 7.6-7.12:十全十美(十全十美)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>1019572719528</t>
+        </is>
+      </c>
+      <c r="B33" s="32" t="inlineStr">
+        <is>
+          <t>杯面,袋面其他</t>
+        </is>
+      </c>
+      <c r="C33" s="32" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>5.11-5.17:袋面其他(日韩袋面); 6.29-7.5:袋面其他(日韩袋面); 7.13-7.19:袋面其他(日韩袋面); 7.6-7.12:杯面(杯面混搭)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>三、对结论的影响与处理</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="26" t="inlineStr">
+        <is>
+          <t>1. ID周利润、店铺周汇总、TOP亏损ID（按ID）：无金额矛盾，可继续用。</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="26" t="inlineStr">
+        <is>
+          <t>2. 「原味大大/巴东」等按定位过滤的专题：已同义归一；但仍按当周挂品计入，跨周改品ID不会被强行改写品名。</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="26" t="inlineStr">
+        <is>
+          <t>3. 「近周回落归因」中若ID两周品类不同，已标注「串品:A→B」，避免把30包/巴东等不同品当成同品环比。</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="26" t="inlineStr">
+        <is>
+          <t>4. 06全量ID表新增「跨周改品」列；主定位仍为成交加权众数（例如0806主标30包，但7.6当周实际是巴东）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="inlineStr">
+        <is>
+          <t>5. 巴东费率结论已按实测周修正，不再写死32%–38%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26" t="inlineStr">
+        <is>
+          <t>6. 使用前请打开Excel并开启自动计算（其他费用/推广后为公式）。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1805,7 +2521,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>金额为SUMIFS；变化=后周-前周。</t>
+          <t>金额为SUMIFS；变化=后周-前周。若定位含「串品」，表示该ID两周挂品不同，环比仅作ID视角参考，不能当同品解读。</t>
         </is>
       </c>
     </row>
@@ -1896,12 +2612,12 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>30包</t>
+          <t>串品:巴东→30包</t>
         </is>
       </c>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>进口营多捞面一整箱30包网红速食方便面宿舍速食泡面干拌面拉面</t>
+          <t>[非同品对比] 进口营多捞面一整箱30包网红速食方便面宿舍速食泡面干拌面拉面</t>
         </is>
       </c>
       <c r="E7" s="12">
@@ -1960,12 +2676,12 @@
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>12包</t>
+          <t>串品:巴东→12包</t>
         </is>
       </c>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>营多印尼进口营多捞面方便面火鸡面干拌面12包宿舍速食泡面夜宵</t>
+          <t>[非同品对比] 营多印尼进口营多捞面方便面火鸡面干拌面12包宿舍速食泡面夜宵</t>
         </is>
       </c>
       <c r="E9" s="12">
@@ -1992,12 +2708,12 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>15包</t>
+          <t>串品:15包→原味大大</t>
         </is>
       </c>
       <c r="D10" s="17" t="inlineStr">
         <is>
-          <t>进口营多捞面15包Indomie方便面干拌面夜宵方便速食五连包85g*5</t>
+          <t>[非同品对比] 印尼进口大大包营多原味捞面5包干拌面速食超大包方便面速食宵夜</t>
         </is>
       </c>
       <c r="E10" s="12">
@@ -2024,12 +2740,12 @@
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>巴东牛肉</t>
+          <t>串品:巴东→原味大大</t>
         </is>
       </c>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>营多进口新口味巴东炖牛肉味捞面印尼料理方便面泡面捞面夜宵速食</t>
+          <t>[非同品对比] indomie印尼进口营多原味大大包129g捞面方便面速食食品宵夜小吃</t>
         </is>
       </c>
       <c r="E11" s="12">
@@ -2292,12 +3008,12 @@
       </c>
       <c r="C21" s="11" t="inlineStr">
         <is>
-          <t>杯面次链接</t>
+          <t>串品:原味大大→巴东</t>
         </is>
       </c>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>营多捞面杯装方便面泡面速食干拌面原味整箱批发印尼进口桶装拌面</t>
+          <t>[非同品对比] 营多进口新口味巴东炖牛肉味捞面印尼料理方便面泡面捞面夜宵速食</t>
         </is>
       </c>
       <c r="E21" s="12">
@@ -2356,12 +3072,12 @@
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>原味大包</t>
+          <t>串品:原味大大→巴东</t>
         </is>
       </c>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>印尼进口大大包营多原味捞面5包干拌面速食超大包方便面速食宵夜</t>
+          <t>[非同品对比] 【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
         </is>
       </c>
       <c r="E23" s="12">
@@ -4161,14 +4877,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>原味大大包专题（定位=大大/原味大包 · 公式）</t>
+          <t>原味大大包专题（定位=原味大包；已将源「大大」同义归一）</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>按周SUMIFS；不再合并7.20-8.2双周。</t>
+          <t>按周SUMIFS（定位=大大/原味大包）。注意：同一商品ID可能跨周改挂品类，本表按「当周定位」计入，不等于该ID全期都是大大包。详见08。</t>
         </is>
       </c>
     </row>
@@ -4228,23 +4944,23 @@
         </is>
       </c>
       <c r="B6" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A6,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C6" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A6,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D6" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A6,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E6" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A6,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F6" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A6,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G6" s="12">
@@ -4252,7 +4968,7 @@
         <v/>
       </c>
       <c r="H6" s="18">
-        <f>COUNTIFS(数据源!A:A,A6,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A6,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A6,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4263,23 +4979,23 @@
         </is>
       </c>
       <c r="B7" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A7,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C7" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A7,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D7" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A7,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E7" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A7,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F7" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A7,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G7" s="12">
@@ -4287,7 +5003,7 @@
         <v/>
       </c>
       <c r="H7" s="18">
-        <f>COUNTIFS(数据源!A:A,A7,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A7,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A7,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4298,23 +5014,23 @@
         </is>
       </c>
       <c r="B8" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A8,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C8" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A8,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D8" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A8,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E8" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A8,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F8" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A8,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G8" s="12">
@@ -4322,7 +5038,7 @@
         <v/>
       </c>
       <c r="H8" s="18">
-        <f>COUNTIFS(数据源!A:A,A8,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A8,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A8,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4333,23 +5049,23 @@
         </is>
       </c>
       <c r="B9" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A9,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C9" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A9,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D9" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A9,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E9" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A9,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F9" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A9,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G9" s="12">
@@ -4357,7 +5073,7 @@
         <v/>
       </c>
       <c r="H9" s="18">
-        <f>COUNTIFS(数据源!A:A,A9,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A9,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A9,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4368,23 +5084,23 @@
         </is>
       </c>
       <c r="B10" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A10,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C10" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A10,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D10" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A10,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E10" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A10,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F10" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A10,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G10" s="12">
@@ -4392,7 +5108,7 @@
         <v/>
       </c>
       <c r="H10" s="18">
-        <f>COUNTIFS(数据源!A:A,A10,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A10,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A10,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4403,23 +5119,23 @@
         </is>
       </c>
       <c r="B11" s="12">
-        <f>SUMIFS(数据源!E:E,数据源!A:A,A11,数据源!C:C,"大大")+SUMIFS(数据源!E:E,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!E:E,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="C11" s="12">
-        <f>SUMIFS(数据源!X:X,数据源!A:A,A11,数据源!C:C,"大大")+SUMIFS(数据源!X:X,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!X:X,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="D11" s="12">
-        <f>SUMIFS(数据源!P:P,数据源!A:A,A11,数据源!C:C,"大大")+SUMIFS(数据源!P:P,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!P:P,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="E11" s="13">
-        <f>SUMIFS(数据源!W:W,数据源!A:A,A11,数据源!C:C,"大大")+SUMIFS(数据源!W:W,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!W:W,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="F11" s="12">
-        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A11,数据源!C:C,"大大")+SUMIFS(数据源!AB:AB,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>SUMIFS(数据源!AB:AB,数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
       <c r="G11" s="12">
@@ -4427,7 +5143,7 @@
         <v/>
       </c>
       <c r="H11" s="18">
-        <f>COUNTIFS(数据源!A:A,A11,数据源!C:C,"大大")+COUNTIFS(数据源!A:A,A11,数据源!C:C,"原味大包")</f>
+        <f>COUNTIFS(数据源!A:A,A11,数据源!C:C,"原味大包")</f>
         <v/>
       </c>
     </row>
@@ -4498,7 +5214,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
@@ -4540,7 +5256,7 @@
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D17" s="17" t="inlineStr">
@@ -5210,7 +5926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:O56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5239,7 +5955,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>定位/名称取自数据源高频定位；各周与变化列为公式。</t>
+          <t>定位/名称=成交加权主标签；「跨周改品」=数据源中同一ID出现多个品类家族。各周利润为公式。</t>
         </is>
       </c>
     </row>
@@ -5259,57 +5975,62 @@
           <t>商品名称</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>跨周改品</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>5.11-5.17</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>5.25-5.31</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>6.15-6.21</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>6.22-6.28</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>6.29-7.5</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>7.6-7.12</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>7.13-7.19</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>7.20-7.26</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>7.27-8.2</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="24" t="inlineStr">
         <is>
           <t>7.6→7.13变化</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="24" t="inlineStr">
         <is>
           <t>7.13→7.20变化</t>
         </is>
@@ -5331,50 +6052,55 @@
           <t>营多捞面印尼进口Indomie网红夜宵早餐方便面火鸡面泡面拌面</t>
         </is>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E5" s="12">
+      <c r="F5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F5" s="12">
+      <c r="G5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G5" s="12">
+      <c r="H5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H5" s="12">
+      <c r="I5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I5" s="12">
+      <c r="J5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J5" s="12">
+      <c r="K5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K5" s="12">
+      <c r="L5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L5" s="12">
+      <c r="M5" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A5,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M5" s="13">
-        <f>J5-I5</f>
         <v/>
       </c>
       <c r="N5" s="13">
         <f>K5-J5</f>
         <v/>
       </c>
+      <c r="O5" s="13">
+        <f>L5-K5</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
@@ -5392,50 +6118,55 @@
           <t>印尼营多捞面进口网红泡面袋装方便面速食食品拉面火鸡面拌面整箱</t>
         </is>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E6" s="12">
+      <c r="F6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F6" s="12">
+      <c r="G6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G6" s="12">
+      <c r="H6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H6" s="12">
+      <c r="I6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I6" s="12">
+      <c r="J6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J6" s="12">
+      <c r="K6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K6" s="12">
+      <c r="L6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L6" s="12">
+      <c r="M6" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A6,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M6" s="13">
-        <f>J6-I6</f>
         <v/>
       </c>
       <c r="N6" s="13">
         <f>K6-J6</f>
         <v/>
       </c>
+      <c r="O6" s="13">
+        <f>L6-K6</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -5453,50 +6184,55 @@
           <t>印尼进口indomie营多捞面杯面速食泡面干拌面盒桶装方便面火鸡面</t>
         </is>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F7" s="12">
+      <c r="G7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G7" s="12">
+      <c r="H7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H7" s="12">
+      <c r="I7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I7" s="12">
+      <c r="J7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J7" s="12">
+      <c r="K7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K7" s="12">
+      <c r="L7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L7" s="12">
+      <c r="M7" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A7,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M7" s="13">
-        <f>J7-I7</f>
         <v/>
       </c>
       <c r="N7" s="13">
         <f>K7-J7</f>
         <v/>
       </c>
+      <c r="O7" s="13">
+        <f>L7-K7</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
@@ -5514,50 +6250,55 @@
           <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
         </is>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E8" s="12">
+      <c r="F8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F8" s="12">
+      <c r="G8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G8" s="12">
+      <c r="H8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H8" s="12">
+      <c r="I8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I8" s="12">
+      <c r="J8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J8" s="12">
+      <c r="K8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K8" s="12">
+      <c r="L8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L8" s="12">
+      <c r="M8" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A8,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="13">
-        <f>J8-I8</f>
         <v/>
       </c>
       <c r="N8" s="13">
         <f>K8-J8</f>
         <v/>
       </c>
+      <c r="O8" s="13">
+        <f>L8-K8</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
@@ -5575,50 +6316,55 @@
           <t>进口营多捞面一整箱30包网红速食方便面宿舍速食泡面干拌面拉面</t>
         </is>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>30包,巴东</t>
+        </is>
+      </c>
+      <c r="E9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F9" s="12">
+      <c r="G9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G9" s="12">
+      <c r="H9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H9" s="12">
+      <c r="I9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I9" s="12">
+      <c r="J9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J9" s="12">
+      <c r="K9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K9" s="12">
+      <c r="L9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L9" s="12">
+      <c r="M9" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A9,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="13">
-        <f>J9-I9</f>
         <v/>
       </c>
       <c r="N9" s="13">
         <f>K9-J9</f>
         <v/>
       </c>
+      <c r="O9" s="13">
+        <f>L9-K9</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -5636,50 +6382,55 @@
           <t>进口营多原味杯面日式杯面韩式杯面泡面方便面汤面宿舍速食夜宵</t>
         </is>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>原味大大,杯面</t>
+        </is>
+      </c>
+      <c r="E10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E10" s="12">
+      <c r="F10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F10" s="12">
+      <c r="G10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G10" s="12">
+      <c r="H10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H10" s="12">
+      <c r="I10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I10" s="12">
+      <c r="J10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J10" s="12">
+      <c r="K10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K10" s="12">
+      <c r="L10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L10" s="12">
+      <c r="M10" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A10,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M10" s="13">
-        <f>J10-I10</f>
         <v/>
       </c>
       <c r="N10" s="13">
         <f>K10-J10</f>
         <v/>
       </c>
+      <c r="O10" s="13">
+        <f>L10-K10</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
@@ -5697,50 +6448,55 @@
           <t>营多捞面日式鸡肉汤面原味辛辣味袋装泡面方便面速食宿舍夜宵食品</t>
         </is>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>巴东,袋面其他</t>
+        </is>
+      </c>
+      <c r="E11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E11" s="12">
+      <c r="F11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F11" s="12">
+      <c r="G11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G11" s="12">
+      <c r="H11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H11" s="12">
+      <c r="I11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I11" s="12">
+      <c r="J11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J11" s="12">
+      <c r="K11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K11" s="12">
+      <c r="L11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L11" s="12">
+      <c r="M11" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A11,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M11" s="13">
-        <f>J11-I11</f>
         <v/>
       </c>
       <c r="N11" s="13">
         <f>K11-J11</f>
         <v/>
       </c>
+      <c r="O11" s="13">
+        <f>L11-K11</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
@@ -5758,50 +6514,55 @@
           <t>印尼营多捞面干拌面一整箱24袋装批发泡面宿舍速食方便面火鸡面</t>
         </is>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E12" s="12">
+      <c r="F12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F12" s="12">
+      <c r="G12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G12" s="12">
+      <c r="H12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H12" s="12">
+      <c r="I12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I12" s="12">
+      <c r="J12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J12" s="12">
+      <c r="K12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K12" s="12">
+      <c r="L12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L12" s="12">
+      <c r="M12" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A12,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M12" s="13">
-        <f>J12-I12</f>
         <v/>
       </c>
       <c r="N12" s="13">
         <f>K12-J12</f>
         <v/>
       </c>
+      <c r="O12" s="13">
+        <f>L12-K12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -5819,50 +6580,55 @@
           <t>营多捞面杯装方便面泡面速食干拌面原味整箱批发印尼进口桶装拌面</t>
         </is>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>原味大大,巴东,杯面</t>
+        </is>
+      </c>
+      <c r="E13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E13" s="12">
+      <c r="F13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F13" s="12">
+      <c r="G13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G13" s="12">
+      <c r="H13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H13" s="12">
+      <c r="I13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I13" s="12">
+      <c r="J13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J13" s="12">
+      <c r="K13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K13" s="12">
+      <c r="L13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L13" s="12">
+      <c r="M13" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A13,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M13" s="13">
-        <f>J13-I13</f>
         <v/>
       </c>
       <c r="N13" s="13">
         <f>K13-J13</f>
         <v/>
       </c>
+      <c r="O13" s="13">
+        <f>L13-K13</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
@@ -5880,50 +6646,55 @@
           <t>进口营多捞面15包Indomie方便面干拌面夜宵方便速食五连包85g*5</t>
         </is>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>15包,原味大大</t>
+        </is>
+      </c>
+      <c r="E14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E14" s="12">
+      <c r="F14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F14" s="12">
+      <c r="G14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G14" s="12">
+      <c r="H14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H14" s="12">
+      <c r="I14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I14" s="12">
+      <c r="J14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J14" s="12">
+      <c r="K14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K14" s="12">
+      <c r="L14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L14" s="12">
+      <c r="M14" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A14,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M14" s="13">
-        <f>J14-I14</f>
         <v/>
       </c>
       <c r="N14" s="13">
         <f>K14-J14</f>
         <v/>
       </c>
+      <c r="O14" s="13">
+        <f>L14-K14</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
@@ -5941,50 +6712,55 @@
           <t>营多进口新口味巴东炖牛肉味捞面印尼料理方便面泡面捞面夜宵速食</t>
         </is>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>原味大大,巴东</t>
+        </is>
+      </c>
+      <c r="E15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E15" s="12">
+      <c r="F15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F15" s="12">
+      <c r="G15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G15" s="12">
+      <c r="H15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H15" s="12">
+      <c r="I15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I15" s="12">
+      <c r="J15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J15" s="12">
+      <c r="K15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K15" s="12">
+      <c r="L15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L15" s="12">
+      <c r="M15" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A15,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M15" s="13">
-        <f>J15-I15</f>
         <v/>
       </c>
       <c r="N15" s="13">
         <f>K15-J15</f>
         <v/>
       </c>
+      <c r="O15" s="13">
+        <f>L15-K15</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
@@ -6002,50 +6778,55 @@
           <t>营多捞面甜辣炸鸡火鸡面辣蘑菇泡面方便面速食干拌面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E16" s="12">
+      <c r="F16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F16" s="12">
+      <c r="G16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G16" s="12">
+      <c r="H16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H16" s="12">
+      <c r="I16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I16" s="12">
+      <c r="J16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J16" s="12">
+      <c r="K16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K16" s="12">
+      <c r="L16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L16" s="12">
+      <c r="M16" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A16,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M16" s="13">
-        <f>J16-I16</f>
         <v/>
       </c>
       <c r="N16" s="13">
         <f>K16-J16</f>
         <v/>
       </c>
+      <c r="O16" s="13">
+        <f>L16-K16</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
@@ -6063,50 +6844,55 @@
           <t>新品营多捞面韩式辣蘑菇汤面泡面方便面速食干拌面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E17" s="12">
+      <c r="F17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F17" s="12">
+      <c r="G17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G17" s="12">
+      <c r="H17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H17" s="12">
+      <c r="I17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I17" s="12">
+      <c r="J17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J17" s="12">
+      <c r="K17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K17" s="12">
+      <c r="L17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L17" s="12">
+      <c r="M17" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A17,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M17" s="13">
-        <f>J17-I17</f>
         <v/>
       </c>
       <c r="N17" s="13">
         <f>K17-J17</f>
         <v/>
       </c>
+      <c r="O17" s="13">
+        <f>L17-K17</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
@@ -6124,50 +6910,55 @@
           <t>进口营多正品捞面日式鸡肉鸡汤辛辣味袋装泡面辣味速食方便面汤面</t>
         </is>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E18" s="12">
+      <c r="F18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F18" s="12">
+      <c r="G18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G18" s="12">
+      <c r="H18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H18" s="12">
+      <c r="I18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I18" s="12">
+      <c r="J18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J18" s="12">
+      <c r="K18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K18" s="12">
+      <c r="L18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L18" s="12">
+      <c r="M18" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A18,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M18" s="13">
-        <f>J18-I18</f>
         <v/>
       </c>
       <c r="N18" s="13">
         <f>K18-J18</f>
         <v/>
       </c>
+      <c r="O18" s="13">
+        <f>L18-K18</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
@@ -6185,50 +6976,55 @@
           <t>【天猫U选】indomie营多大骨牛肉味捞面拌面5包</t>
         </is>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>【U选】原味5,杯面</t>
+        </is>
+      </c>
+      <c r="E19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E19" s="12">
+      <c r="F19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F19" s="12">
+      <c r="G19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G19" s="12">
+      <c r="H19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H19" s="12">
+      <c r="I19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I19" s="12">
+      <c r="J19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J19" s="12">
+      <c r="K19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K19" s="12">
+      <c r="L19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L19" s="12">
+      <c r="M19" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A19,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="13">
-        <f>J19-I19</f>
         <v/>
       </c>
       <c r="N19" s="13">
         <f>K19-J19</f>
         <v/>
       </c>
+      <c r="O19" s="13">
+        <f>L19-K19</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
@@ -6246,50 +7042,55 @@
           <t>营多捞面多口味袋装泡面拌面速食面干拌面方便面宿舍宵夜速食旅行</t>
         </is>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>组合,袋面其他</t>
+        </is>
+      </c>
+      <c r="E20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E20" s="12">
+      <c r="F20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F20" s="12">
+      <c r="G20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G20" s="12">
+      <c r="H20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H20" s="12">
+      <c r="I20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I20" s="12">
+      <c r="J20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J20" s="12">
+      <c r="K20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K20" s="12">
+      <c r="L20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L20" s="12">
+      <c r="M20" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A20,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="13">
-        <f>J20-I20</f>
         <v/>
       </c>
       <c r="N20" s="13">
         <f>K20-J20</f>
         <v/>
       </c>
+      <c r="O20" s="13">
+        <f>L20-K20</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
@@ -6307,50 +7108,55 @@
           <t>进口正品意面风味奶香番茄牛肉味意式拌面营多捞面早餐儿童宝妈餐</t>
         </is>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E21" s="12">
+      <c r="F21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F21" s="12">
+      <c r="G21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G21" s="12">
+      <c r="H21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H21" s="12">
+      <c r="I21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I21" s="12">
+      <c r="J21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J21" s="12">
+      <c r="K21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K21" s="12">
+      <c r="L21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L21" s="12">
+      <c r="M21" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A21,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="13">
-        <f>J21-I21</f>
         <v/>
       </c>
       <c r="N21" s="13">
         <f>K21-J21</f>
         <v/>
       </c>
+      <c r="O21" s="13">
+        <f>L21-K21</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
@@ -6368,50 +7174,55 @@
           <t>indomie印尼进口营多原味大大包129g捞面方便面速食食品宵夜小吃</t>
         </is>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E22" s="12">
+      <c r="F22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F22" s="12">
+      <c r="G22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G22" s="12">
+      <c r="H22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H22" s="12">
+      <c r="I22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I22" s="12">
+      <c r="J22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J22" s="12">
+      <c r="K22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K22" s="12">
+      <c r="L22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L22" s="12">
+      <c r="M22" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A22,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="13">
-        <f>J22-I22</f>
         <v/>
       </c>
       <c r="N22" s="13">
         <f>K22-J22</f>
         <v/>
       </c>
+      <c r="O22" s="13">
+        <f>L22-K22</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -6429,50 +7240,55 @@
           <t>新品营多捞面韩式辣蘑菇汤面泡面方便面速食干拌面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E23" s="12">
+      <c r="F23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F23" s="12">
+      <c r="G23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G23" s="12">
+      <c r="H23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H23" s="12">
+      <c r="I23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I23" s="12">
+      <c r="J23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J23" s="12">
+      <c r="K23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K23" s="12">
+      <c r="L23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L23" s="12">
+      <c r="M23" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A23,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="13">
-        <f>J23-I23</f>
         <v/>
       </c>
       <c r="N23" s="13">
         <f>K23-J23</f>
         <v/>
       </c>
+      <c r="O23" s="13">
+        <f>L23-K23</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
@@ -6490,50 +7306,55 @@
           <t>营多捞面汤面清香牛肉味方便面泡面速食食品泡面拉面整箱旅行宿舍</t>
         </is>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E24" s="12">
+      <c r="F24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F24" s="12">
+      <c r="G24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G24" s="12">
+      <c r="H24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H24" s="12">
+      <c r="I24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I24" s="12">
+      <c r="J24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J24" s="12">
+      <c r="K24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K24" s="12">
+      <c r="L24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L24" s="12">
+      <c r="M24" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A24,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="13">
-        <f>J24-I24</f>
         <v/>
       </c>
       <c r="N24" s="13">
         <f>K24-J24</f>
         <v/>
       </c>
+      <c r="O24" s="13">
+        <f>L24-K24</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
@@ -6551,50 +7372,55 @@
           <t>【天猫U选】indomie营多捞面辣火鸡味日式鸡肉原味杯面</t>
         </is>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E25" s="12">
+      <c r="F25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F25" s="12">
+      <c r="G25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G25" s="12">
+      <c r="H25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H25" s="12">
+      <c r="I25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I25" s="12">
+      <c r="J25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J25" s="12">
+      <c r="K25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K25" s="12">
+      <c r="L25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L25" s="12">
+      <c r="M25" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A25,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M25" s="13">
-        <f>J25-I25</f>
         <v/>
       </c>
       <c r="N25" s="13">
         <f>K25-J25</f>
         <v/>
       </c>
+      <c r="O25" s="13">
+        <f>L25-K25</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
@@ -6612,50 +7438,55 @@
           <t>【天猫U选】indomie营多捞面辣蘑菇味日式辣味杯面</t>
         </is>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>十全十美,杯面</t>
+        </is>
+      </c>
+      <c r="E26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E26" s="12">
+      <c r="F26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F26" s="12">
+      <c r="G26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G26" s="12">
+      <c r="H26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H26" s="12">
+      <c r="I26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I26" s="12">
+      <c r="J26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J26" s="12">
+      <c r="K26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K26" s="12">
+      <c r="L26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L26" s="12">
+      <c r="M26" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A26,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M26" s="13">
-        <f>J26-I26</f>
         <v/>
       </c>
       <c r="N26" s="13">
         <f>K26-J26</f>
         <v/>
       </c>
+      <c r="O26" s="13">
+        <f>L26-K26</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
@@ -6673,50 +7504,55 @@
           <t>进口营多大骨番茄牛肉味营多捞面意式泡面宿舍宿舍宵夜速食方便面</t>
         </is>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E27" s="12">
+      <c r="F27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F27" s="12">
+      <c r="G27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G27" s="12">
+      <c r="H27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H27" s="12">
+      <c r="I27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I27" s="12">
+      <c r="J27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J27" s="12">
+      <c r="K27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K27" s="12">
+      <c r="L27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L27" s="12">
+      <c r="M27" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A27,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M27" s="13">
-        <f>J27-I27</f>
         <v/>
       </c>
       <c r="N27" s="13">
         <f>K27-J27</f>
         <v/>
       </c>
+      <c r="O27" s="13">
+        <f>L27-K27</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
@@ -6734,50 +7570,55 @@
           <t>进口营多捞面汤面拌面七口味混合方便面速拉面宿舍拌面泡面食食品</t>
         </is>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>七口味混搭,杯面</t>
+        </is>
+      </c>
+      <c r="E28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E28" s="12">
+      <c r="F28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F28" s="12">
+      <c r="G28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G28" s="12">
+      <c r="H28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H28" s="12">
+      <c r="I28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I28" s="12">
+      <c r="J28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J28" s="12">
+      <c r="K28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K28" s="12">
+      <c r="L28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L28" s="12">
+      <c r="M28" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A28,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M28" s="13">
-        <f>J28-I28</f>
         <v/>
       </c>
       <c r="N28" s="13">
         <f>K28-J28</f>
         <v/>
       </c>
+      <c r="O28" s="13">
+        <f>L28-K28</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -6795,50 +7636,55 @@
           <t>营多捞面杯装方便面泡面速食干拌面原味整箱批发印尼进口桶装拌面</t>
         </is>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E29" s="12">
+      <c r="F29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F29" s="12">
+      <c r="G29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G29" s="12">
+      <c r="H29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H29" s="12">
+      <c r="I29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="J29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="K29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="L29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="M29" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A29,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M29" s="13">
-        <f>J29-I29</f>
         <v/>
       </c>
       <c r="N29" s="13">
         <f>K29-J29</f>
         <v/>
       </c>
+      <c r="O29" s="13">
+        <f>L29-K29</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
@@ -6856,50 +7702,55 @@
           <t>营多捞面韩式甜辣炸鸡辣蘑菇杯面方便面拌面泡面宿舍速食面</t>
         </is>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E30" s="12">
+      <c r="F30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F30" s="12">
+      <c r="G30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G30" s="12">
+      <c r="H30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H30" s="12">
+      <c r="I30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I30" s="12">
+      <c r="J30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J30" s="12">
+      <c r="K30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K30" s="12">
+      <c r="L30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L30" s="12">
+      <c r="M30" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A30,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M30" s="13">
-        <f>J30-I30</f>
         <v/>
       </c>
       <c r="N30" s="13">
         <f>K30-J30</f>
         <v/>
       </c>
+      <c r="O30" s="13">
+        <f>L30-K30</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
@@ -6917,50 +7768,55 @@
           <t>营多韩式火鸡面袋装拌面干拌面泡面方便面速食面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E31" s="12">
+      <c r="F31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F31" s="12">
+      <c r="G31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G31" s="12">
+      <c r="H31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H31" s="12">
+      <c r="I31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I31" s="12">
+      <c r="J31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J31" s="12">
+      <c r="K31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K31" s="12">
+      <c r="L31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L31" s="12">
+      <c r="M31" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A31,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M31" s="13">
-        <f>J31-I31</f>
         <v/>
       </c>
       <c r="N31" s="13">
         <f>K31-J31</f>
         <v/>
       </c>
+      <c r="O31" s="13">
+        <f>L31-K31</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
@@ -6978,50 +7834,55 @@
           <t>营多印尼进口营多捞面方便面火鸡面干拌面10包宿舍速食泡面夜宵</t>
         </is>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E32" s="12">
+      <c r="F32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F32" s="12">
+      <c r="G32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G32" s="12">
+      <c r="H32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H32" s="12">
+      <c r="I32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I32" s="12">
+      <c r="J32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J32" s="12">
+      <c r="K32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K32" s="12">
+      <c r="L32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L32" s="12">
+      <c r="M32" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A32,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M32" s="13">
-        <f>J32-I32</f>
         <v/>
       </c>
       <c r="N32" s="13">
         <f>K32-J32</f>
         <v/>
       </c>
+      <c r="O32" s="13">
+        <f>L32-K32</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
@@ -7039,50 +7900,55 @@
           <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
         </is>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E33" s="12">
+      <c r="F33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F33" s="12">
+      <c r="G33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G33" s="12">
+      <c r="H33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H33" s="12">
+      <c r="I33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="J33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="K33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="L33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="M33" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A33,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M33" s="13">
-        <f>J33-I33</f>
         <v/>
       </c>
       <c r="N33" s="13">
         <f>K33-J33</f>
         <v/>
       </c>
+      <c r="O33" s="13">
+        <f>L33-K33</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
@@ -7100,50 +7966,55 @@
           <t>印尼进口营多捞面杯面原味甜辣蘑菇味整箱速食拌面拉面泡面方便面</t>
         </is>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E34" s="12">
+      <c r="F34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F34" s="12">
+      <c r="G34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G34" s="12">
+      <c r="H34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H34" s="12">
+      <c r="I34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I34" s="12">
+      <c r="J34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J34" s="12">
+      <c r="K34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K34" s="12">
+      <c r="L34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L34" s="12">
+      <c r="M34" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A34,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M34" s="13">
-        <f>J34-I34</f>
         <v/>
       </c>
       <c r="N34" s="13">
         <f>K34-J34</f>
         <v/>
       </c>
+      <c r="O34" s="13">
+        <f>L34-K34</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
@@ -7153,50 +8024,55 @@
       </c>
       <c r="B35" s="11" t="inlineStr"/>
       <c r="C35" s="17" t="inlineStr"/>
-      <c r="D35" s="12">
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E35" s="12">
+      <c r="F35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F35" s="12">
+      <c r="G35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G35" s="12">
+      <c r="H35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H35" s="12">
+      <c r="I35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I35" s="12">
+      <c r="J35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J35" s="12">
+      <c r="K35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K35" s="12">
+      <c r="L35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L35" s="12">
+      <c r="M35" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A35,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M35" s="13">
-        <f>J35-I35</f>
         <v/>
       </c>
       <c r="N35" s="13">
         <f>K35-J35</f>
         <v/>
       </c>
+      <c r="O35" s="13">
+        <f>L35-K35</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
@@ -7214,50 +8090,55 @@
           <t>营多捞面韩式火鸡面辣蘑菇汤面袋装泡面辣味速食方便面宿舍宵夜面</t>
         </is>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E36" s="12">
+      <c r="F36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F36" s="12">
+      <c r="G36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G36" s="12">
+      <c r="H36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H36" s="12">
+      <c r="I36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I36" s="12">
+      <c r="J36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J36" s="12">
+      <c r="K36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K36" s="12">
+      <c r="L36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L36" s="12">
+      <c r="M36" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A36,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M36" s="13">
-        <f>J36-I36</f>
         <v/>
       </c>
       <c r="N36" s="13">
         <f>K36-J36</f>
         <v/>
       </c>
+      <c r="O36" s="13">
+        <f>L36-K36</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
@@ -7267,50 +8148,55 @@
       </c>
       <c r="B37" s="11" t="inlineStr"/>
       <c r="C37" s="17" t="inlineStr"/>
-      <c r="D37" s="12">
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E37" s="12">
+      <c r="F37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F37" s="12">
+      <c r="G37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G37" s="12">
+      <c r="H37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H37" s="12">
+      <c r="I37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I37" s="12">
+      <c r="J37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J37" s="12">
+      <c r="K37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K37" s="12">
+      <c r="L37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L37" s="12">
+      <c r="M37" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A37,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M37" s="13">
-        <f>J37-I37</f>
         <v/>
       </c>
       <c r="N37" s="13">
         <f>K37-J37</f>
         <v/>
       </c>
+      <c r="O37" s="13">
+        <f>L37-K37</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="11" t="inlineStr">
@@ -7320,7 +8206,7 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="C38" s="17" t="inlineStr">
@@ -7328,50 +8214,55 @@
           <t>【新口味】印尼进口营多捞面巴东炖牛肉味泡面方便面宿舍速食宵夜</t>
         </is>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E38" s="12">
+      <c r="F38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F38" s="12">
+      <c r="G38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G38" s="12">
+      <c r="H38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H38" s="12">
+      <c r="I38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I38" s="12">
+      <c r="J38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J38" s="12">
+      <c r="K38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K38" s="12">
+      <c r="L38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L38" s="12">
+      <c r="M38" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A38,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M38" s="13">
-        <f>J38-I38</f>
         <v/>
       </c>
       <c r="N38" s="13">
         <f>K38-J38</f>
         <v/>
       </c>
+      <c r="O38" s="13">
+        <f>L38-K38</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -7389,50 +8280,55 @@
           <t>进口营多捞面汤面拌面六口味混合方便面速食食品泡面</t>
         </is>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E39" s="12">
+      <c r="F39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F39" s="12">
+      <c r="G39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G39" s="12">
+      <c r="H39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H39" s="12">
+      <c r="I39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I39" s="12">
+      <c r="J39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J39" s="12">
+      <c r="K39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K39" s="12">
+      <c r="L39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L39" s="12">
+      <c r="M39" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A39,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M39" s="13">
-        <f>J39-I39</f>
         <v/>
       </c>
       <c r="N39" s="13">
         <f>K39-J39</f>
         <v/>
       </c>
+      <c r="O39" s="13">
+        <f>L39-K39</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="11" t="inlineStr">
@@ -7450,50 +8346,55 @@
           <t>营多捞面原味番茄牛肉袋装泡面汤面干拌面方便面宿舍速食旅行宵夜</t>
         </is>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E40" s="12">
+      <c r="F40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F40" s="12">
+      <c r="G40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G40" s="12">
+      <c r="H40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H40" s="12">
+      <c r="I40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I40" s="12">
+      <c r="J40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J40" s="12">
+      <c r="K40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K40" s="12">
+      <c r="L40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L40" s="12">
+      <c r="M40" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A40,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M40" s="13">
-        <f>J40-I40</f>
         <v/>
       </c>
       <c r="N40" s="13">
         <f>K40-J40</f>
         <v/>
       </c>
+      <c r="O40" s="13">
+        <f>L40-K40</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
@@ -7511,50 +8412,55 @@
           <t>INDOMIE营多日式杯面原味经典泡面整箱批发速食宿舍旅行宵夜宿舍</t>
         </is>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E41" s="12">
+      <c r="F41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F41" s="12">
+      <c r="G41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G41" s="12">
+      <c r="H41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H41" s="12">
+      <c r="I41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I41" s="12">
+      <c r="J41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J41" s="12">
+      <c r="K41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K41" s="12">
+      <c r="L41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L41" s="12">
+      <c r="M41" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A41,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M41" s="13">
-        <f>J41-I41</f>
         <v/>
       </c>
       <c r="N41" s="13">
         <f>K41-J41</f>
         <v/>
       </c>
+      <c r="O41" s="13">
+        <f>L41-K41</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
@@ -7572,50 +8478,55 @@
           <t>进口意大利面风味奶香番茄牛肉味意式营多早餐儿童宝妈家庭餐拌面</t>
         </is>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="25" t="inlineStr">
+        <is>
+          <t>十全十美,番茄,袋面其他</t>
+        </is>
+      </c>
+      <c r="E42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E42" s="12">
+      <c r="F42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F42" s="12">
+      <c r="G42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G42" s="12">
+      <c r="H42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H42" s="12">
+      <c r="I42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I42" s="12">
+      <c r="J42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J42" s="12">
+      <c r="K42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K42" s="12">
+      <c r="L42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L42" s="12">
+      <c r="M42" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A42,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M42" s="13">
-        <f>J42-I42</f>
         <v/>
       </c>
       <c r="N42" s="13">
         <f>K42-J42</f>
         <v/>
       </c>
+      <c r="O42" s="13">
+        <f>L42-K42</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
@@ -7633,50 +8544,55 @@
           <t>新品营多捞面韩式辣蘑菇汤面泡面方便面速食干拌面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="25" t="inlineStr">
+        <is>
+          <t>杯面,袋面其他</t>
+        </is>
+      </c>
+      <c r="E43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E43" s="12">
+      <c r="F43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F43" s="12">
+      <c r="G43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G43" s="12">
+      <c r="H43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H43" s="12">
+      <c r="I43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I43" s="12">
+      <c r="J43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J43" s="12">
+      <c r="K43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K43" s="12">
+      <c r="L43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L43" s="12">
+      <c r="M43" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A43,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M43" s="13">
-        <f>J43-I43</f>
         <v/>
       </c>
       <c r="N43" s="13">
         <f>K43-J43</f>
         <v/>
       </c>
+      <c r="O43" s="13">
+        <f>L43-K43</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
@@ -7694,50 +8610,55 @@
           <t>营多捞面韩式甜辣炸鸡辣蘑菇杯面方便面拌面泡面宿舍速食面</t>
         </is>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E44" s="12">
+      <c r="F44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F44" s="12">
+      <c r="G44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G44" s="12">
+      <c r="H44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H44" s="12">
+      <c r="I44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I44" s="12">
+      <c r="J44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J44" s="12">
+      <c r="K44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K44" s="12">
+      <c r="L44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L44" s="12">
+      <c r="M44" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A44,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M44" s="13">
-        <f>J44-I44</f>
         <v/>
       </c>
       <c r="N44" s="13">
         <f>K44-J44</f>
         <v/>
       </c>
+      <c r="O44" s="13">
+        <f>L44-K44</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
@@ -7755,50 +8676,55 @@
           <t>进口营多原味杯面日式杯面韩式杯面泡面方便面汤面宿舍速食夜宵</t>
         </is>
       </c>
-      <c r="D45" s="12">
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E45" s="12">
+      <c r="F45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F45" s="12">
+      <c r="G45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G45" s="12">
+      <c r="H45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H45" s="12">
+      <c r="I45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I45" s="12">
+      <c r="J45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J45" s="12">
+      <c r="K45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K45" s="12">
+      <c r="L45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L45" s="12">
+      <c r="M45" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A45,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M45" s="13">
-        <f>J45-I45</f>
         <v/>
       </c>
       <c r="N45" s="13">
         <f>K45-J45</f>
         <v/>
       </c>
+      <c r="O45" s="13">
+        <f>L45-K45</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
@@ -7816,50 +8742,55 @@
           <t>营多捞面牛系列大骨牛肉味方便面食品泡面拉面汤面宿舍宵夜旅行</t>
         </is>
       </c>
-      <c r="D46" s="12">
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E46" s="12">
+      <c r="F46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F46" s="12">
+      <c r="G46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G46" s="12">
+      <c r="H46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H46" s="12">
+      <c r="I46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I46" s="12">
+      <c r="J46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J46" s="12">
+      <c r="K46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K46" s="12">
+      <c r="L46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L46" s="12">
+      <c r="M46" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A46,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M46" s="13">
-        <f>J46-I46</f>
         <v/>
       </c>
       <c r="N46" s="13">
         <f>K46-J46</f>
         <v/>
       </c>
+      <c r="O46" s="13">
+        <f>L46-K46</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
@@ -7877,50 +8808,55 @@
           <t>营多韩式甜辣炸鸡火鸡面辣蘑菇杯面拌面泡面方便面速食宵夜旅行</t>
         </is>
       </c>
-      <c r="D47" s="12">
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E47" s="12">
+      <c r="F47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F47" s="12">
+      <c r="G47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G47" s="12">
+      <c r="H47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H47" s="12">
+      <c r="I47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I47" s="12">
+      <c r="J47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J47" s="12">
+      <c r="K47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K47" s="12">
+      <c r="L47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L47" s="12">
+      <c r="M47" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A47,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M47" s="13">
-        <f>J47-I47</f>
         <v/>
       </c>
       <c r="N47" s="13">
         <f>K47-J47</f>
         <v/>
       </c>
+      <c r="O47" s="13">
+        <f>L47-K47</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
@@ -7930,50 +8866,55 @@
       </c>
       <c r="B48" s="11" t="inlineStr"/>
       <c r="C48" s="17" t="inlineStr"/>
-      <c r="D48" s="12">
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E48" s="12">
+      <c r="F48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F48" s="12">
+      <c r="G48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G48" s="12">
+      <c r="H48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H48" s="12">
+      <c r="I48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I48" s="12">
+      <c r="J48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J48" s="12">
+      <c r="K48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K48" s="12">
+      <c r="L48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L48" s="12">
+      <c r="M48" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A48,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M48" s="13">
-        <f>J48-I48</f>
         <v/>
       </c>
       <c r="N48" s="13">
         <f>K48-J48</f>
         <v/>
       </c>
+      <c r="O48" s="13">
+        <f>L48-K48</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
@@ -7991,50 +8932,55 @@
           <t>营多捞面袋装8包装泡面宿舍速食面热干面干拌面方便面火鸡面食品</t>
         </is>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E49" s="12">
+      <c r="F49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F49" s="12">
+      <c r="G49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G49" s="12">
+      <c r="H49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H49" s="12">
+      <c r="I49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I49" s="12">
+      <c r="J49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J49" s="12">
+      <c r="K49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K49" s="12">
+      <c r="L49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L49" s="12">
+      <c r="M49" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A49,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M49" s="13">
-        <f>J49-I49</f>
         <v/>
       </c>
       <c r="N49" s="13">
         <f>K49-J49</f>
         <v/>
       </c>
+      <c r="O49" s="13">
+        <f>L49-K49</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
@@ -8052,50 +8998,55 @@
           <t>营多捞面多口味袋装泡面拌面速食面干拌面方便面速食宵夜宿舍旅行</t>
         </is>
       </c>
-      <c r="D50" s="12">
+      <c r="D50" s="25" t="inlineStr">
+        <is>
+          <t>十全十美,十口味混搭</t>
+        </is>
+      </c>
+      <c r="E50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E50" s="12">
+      <c r="F50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F50" s="12">
+      <c r="G50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G50" s="12">
+      <c r="H50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H50" s="12">
+      <c r="I50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I50" s="12">
+      <c r="J50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J50" s="12">
+      <c r="K50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K50" s="12">
+      <c r="L50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L50" s="12">
+      <c r="M50" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A50,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M50" s="13">
-        <f>J50-I50</f>
         <v/>
       </c>
       <c r="N50" s="13">
         <f>K50-J50</f>
         <v/>
       </c>
+      <c r="O50" s="13">
+        <f>L50-K50</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
@@ -8113,50 +9064,55 @@
           <t>营多捞面八口味袋装泡面拌面速食面干拌面方便面宿舍宵夜速食家用</t>
         </is>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="25" t="inlineStr">
+        <is>
+          <t>杯面,袋面其他</t>
+        </is>
+      </c>
+      <c r="E51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E51" s="12">
+      <c r="F51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F51" s="12">
+      <c r="G51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G51" s="12">
+      <c r="H51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H51" s="12">
+      <c r="I51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I51" s="12">
+      <c r="J51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J51" s="12">
+      <c r="K51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K51" s="12">
+      <c r="L51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L51" s="12">
+      <c r="M51" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A51,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M51" s="13">
-        <f>J51-I51</f>
         <v/>
       </c>
       <c r="N51" s="13">
         <f>K51-J51</f>
         <v/>
       </c>
+      <c r="O51" s="13">
+        <f>L51-K51</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
@@ -8174,50 +9130,55 @@
           <t>进口营多捞面多口味Indomie网红方便面干拌面泡面30包整箱批发面</t>
         </is>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E52" s="12">
+      <c r="F52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F52" s="12">
+      <c r="G52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G52" s="12">
+      <c r="H52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H52" s="12">
+      <c r="I52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I52" s="12">
+      <c r="J52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J52" s="12">
+      <c r="K52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K52" s="12">
+      <c r="L52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L52" s="12">
+      <c r="M52" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A52,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M52" s="13">
-        <f>J52-I52</f>
         <v/>
       </c>
       <c r="N52" s="13">
         <f>K52-J52</f>
         <v/>
       </c>
+      <c r="O52" s="13">
+        <f>L52-K52</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
@@ -8235,50 +9196,55 @@
           <t>营多印尼进口营多捞面方便面火鸡面干拌面20包宿舍速食泡面夜宵</t>
         </is>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E53" s="12">
+      <c r="F53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F53" s="12">
+      <c r="G53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G53" s="12">
+      <c r="H53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H53" s="12">
+      <c r="I53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I53" s="12">
+      <c r="J53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J53" s="12">
+      <c r="K53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K53" s="12">
+      <c r="L53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L53" s="12">
+      <c r="M53" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A53,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M53" s="13">
-        <f>J53-I53</f>
         <v/>
       </c>
       <c r="N53" s="13">
         <f>K53-J53</f>
         <v/>
       </c>
+      <c r="O53" s="13">
+        <f>L53-K53</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
@@ -8296,50 +9262,55 @@
           <t>印尼进口大大包营多原味捞面5包干拌面速食超大包方便面速食宵夜</t>
         </is>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="25" t="inlineStr">
+        <is>
+          <t>原味大大,巴东</t>
+        </is>
+      </c>
+      <c r="E54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E54" s="12">
+      <c r="F54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F54" s="12">
+      <c r="G54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G54" s="12">
+      <c r="H54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H54" s="12">
+      <c r="I54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I54" s="12">
+      <c r="J54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J54" s="12">
+      <c r="K54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K54" s="12">
+      <c r="L54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L54" s="12">
+      <c r="M54" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A54,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M54" s="13">
-        <f>J54-I54</f>
         <v/>
       </c>
       <c r="N54" s="13">
         <f>K54-J54</f>
         <v/>
       </c>
+      <c r="O54" s="13">
+        <f>L54-K54</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
@@ -8357,50 +9328,55 @@
           <t>营多印尼进口营多捞面方便面火鸡面干拌面12包宿舍速食泡面夜宵</t>
         </is>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="25" t="inlineStr">
+        <is>
+          <t>12包,巴东</t>
+        </is>
+      </c>
+      <c r="E55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E55" s="12">
+      <c r="F55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F55" s="12">
+      <c r="G55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G55" s="12">
+      <c r="H55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H55" s="12">
+      <c r="I55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I55" s="12">
+      <c r="J55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J55" s="12">
+      <c r="K55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K55" s="12">
+      <c r="L55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L55" s="12">
+      <c r="M55" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A55,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M55" s="13">
-        <f>J55-I55</f>
         <v/>
       </c>
       <c r="N55" s="13">
         <f>K55-J55</f>
         <v/>
       </c>
+      <c r="O55" s="13">
+        <f>L55-K55</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
@@ -8418,48 +9394,53 @@
           <t>营多捞面干拌面一整箱24袋装批发泡面混搭宿舍速食方便面火鸡面</t>
         </is>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"5.11-5.17"),0)</f>
         <v/>
       </c>
-      <c r="E56" s="12">
+      <c r="F56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"5.25-5.31"),0)</f>
         <v/>
       </c>
-      <c r="F56" s="12">
+      <c r="G56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"6.15-6.21"),0)</f>
         <v/>
       </c>
-      <c r="G56" s="12">
+      <c r="H56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"6.22-6.28"),0)</f>
         <v/>
       </c>
-      <c r="H56" s="12">
+      <c r="I56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"6.29-7.5"),0)</f>
         <v/>
       </c>
-      <c r="I56" s="12">
+      <c r="J56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"7.6-7.12"),0)</f>
         <v/>
       </c>
-      <c r="J56" s="12">
+      <c r="K56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"7.13-7.19"),0)</f>
         <v/>
       </c>
-      <c r="K56" s="12">
+      <c r="L56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"7.20-7.26"),0)</f>
         <v/>
       </c>
-      <c r="L56" s="12">
+      <c r="M56" s="12">
         <f>IFERROR(SUMIFS(数据源!AB:AB,数据源!B:B,$A56,数据源!A:A,"7.27-8.2"),0)</f>
-        <v/>
-      </c>
-      <c r="M56" s="13">
-        <f>J56-I56</f>
         <v/>
       </c>
       <c r="N56" s="13">
         <f>K56-J56</f>
+        <v/>
+      </c>
+      <c r="O56" s="13">
+        <f>L56-K56</f>
         <v/>
       </c>
     </row>
@@ -21326,7 +22307,7 @@
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
@@ -22361,7 +23342,7 @@
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
@@ -22706,7 +23687,7 @@
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
@@ -23051,7 +24032,7 @@
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>巴东</t>
+          <t>巴东牛肉</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
@@ -23166,7 +24147,7 @@
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>大大</t>
+          <t>原味大包</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
@@ -24431,7 +25412,7 @@
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>韩火鸡</t>
+          <t>韩式火鸡</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
@@ -48398,10 +49379,17 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>8. 一致性核对：新增「08-一致性核对」。金额口径PASS；发现同源ID跨周改品（WARN），归因表已标串品；巴东费率旧表述已按周实测修正；定位同义归一（大大/巴东/韩火鸡）。</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>1. 修复：各周亏损TOP5已按数据源重算（其他费用周报校准后），金额/占比用SUMIFS，与数据源一致。</t>
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>9. 06表增加「跨周改品」列；05大大专题说明改为按当周定位，避免与主标签误解。</t>
         </is>
       </c>
     </row>
